--- a/data/Skill.xlsx
+++ b/data/Skill.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GodotProject\2DIncrementGame_Main\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -1236,6 +1241,12 @@
   <sheetPr/>
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="45.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="34.1111111111111" customWidth="1"/>
+    <col min="4" max="4" width="24.8888888888889" customWidth="1"/>
+    <col min="5" max="5" width="23.1111111111111" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">

--- a/data/Skill.xlsx
+++ b/data/Skill.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GodotProject\2DIncrementGame_Main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aaaa\demo\2DIncrementGame_Main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="19200" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Id</t>
   </si>
@@ -76,13 +76,13 @@
     <t>强力射击</t>
   </si>
   <si>
-    <t>提升单次射击的攻击力</t>
+    <t>提升基础攻击伤害</t>
   </si>
   <si>
     <t>分裂射击</t>
   </si>
   <si>
-    <t>一次可以发射多发子弹</t>
+    <t>攻击弹道+1</t>
   </si>
   <si>
     <t>超级子弹</t>
@@ -95,6 +95,42 @@
   </si>
   <si>
     <t>子弹击中边界后能够弹射</t>
+  </si>
+  <si>
+    <t>迅捷施法</t>
+  </si>
+  <si>
+    <t>提升施法速度</t>
+  </si>
+  <si>
+    <t>幸运一击</t>
+  </si>
+  <si>
+    <t>提升攻击暴击概率</t>
+  </si>
+  <si>
+    <t>超强施法</t>
+  </si>
+  <si>
+    <t>提升攻击暴击倍率</t>
+  </si>
+  <si>
+    <t>我还能行</t>
+  </si>
+  <si>
+    <t>增加对局时长</t>
+  </si>
+  <si>
+    <t>引兽香</t>
+  </si>
+  <si>
+    <t>提升刷怪间隔</t>
+  </si>
+  <si>
+    <t>嗜血吸引</t>
+  </si>
+  <si>
+    <t>提升每次刷怪数量</t>
   </si>
 </sst>
 </file>
@@ -1239,13 +1275,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="45.8888888888889" customWidth="1"/>
-    <col min="3" max="3" width="34.1111111111111" customWidth="1"/>
-    <col min="4" max="4" width="24.8888888888889" customWidth="1"/>
-    <col min="5" max="5" width="23.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="45.8916666666667" customWidth="1"/>
+    <col min="3" max="3" width="34.1083333333333" customWidth="1"/>
+    <col min="4" max="4" width="24.8916666666667" customWidth="1"/>
+    <col min="5" max="5" width="23.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1335,7 +1371,7 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1373,6 +1409,108 @@
       </c>
       <c r="E8">
         <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14">
+        <v>9</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/Skill.xlsx
+++ b/data/Skill.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aaaa\demo\2DIncrementGame_Main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GodotProject\2DIncrementGame_Main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="17655"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -1276,12 +1276,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="45.8916666666667" customWidth="1"/>
-    <col min="3" max="3" width="34.1083333333333" customWidth="1"/>
-    <col min="4" max="4" width="24.8916666666667" customWidth="1"/>
-    <col min="5" max="5" width="23.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="45.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="34.1111111111111" customWidth="1"/>
+    <col min="4" max="4" width="24.8888888888889" customWidth="1"/>
+    <col min="5" max="5" width="23.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/data/Skill.xlsx
+++ b/data/Skill.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Id</t>
   </si>
@@ -131,6 +131,12 @@
   </si>
   <si>
     <t>提升每次刷怪数量</t>
+  </si>
+  <si>
+    <t>多重射击</t>
+  </si>
+  <si>
+    <t>攻击轮数+1</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1281,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="45.8888888888889" customWidth="1"/>
@@ -1371,7 +1377,7 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1439,7 +1445,7 @@
         <v>24</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -1456,7 +1462,7 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -1510,7 +1516,24 @@
         <v>9</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
